--- a/docs/Mapping_casi_uso/matrimoni/Matr_012.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_012.xlsx
@@ -893,7 +893,7 @@
     <t>evento.datiEventoMatrimonio.padreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Padre Sposa</t>
@@ -902,7 +902,7 @@
     <t>evento.datiEventoMatrimonio.padreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Madre Sposo</t>
@@ -911,7 +911,7 @@
     <t>evento.datiEventoMatrimonio.madreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Madre Sposa</t>
@@ -920,7 +920,7 @@
     <t>evento.datiEventoMatrimonio.madreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Tutore Sposo</t>
@@ -929,13 +929,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Figlio</t>
@@ -974,7 +974,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Atto Nascita Figlio</t>
@@ -998,13 +998,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Assenso figlio</t>
@@ -1031,7 +1031,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Dati Riconoscimento - Generalità discendenti - Matrimoni</t>
@@ -1178,13 +1178,13 @@
     <t>attoNotarile</t>
   </si>
   <si>
-    <t>Assistenza minore Sposo</t>
+    <t>Assistenza Sposo</t>
   </si>
   <si>
     <t>tipoAssistenteSposo</t>
   </si>
   <si>
-    <t>Assistenza minore Sposa</t>
+    <t>Assistenza Sposa</t>
   </si>
   <si>
     <t>tipoAssistenteSposa</t>
@@ -1288,7 +1288,7 @@
     <col min="4" max="4" width="68.45703125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="33.79296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="218.19921875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="119.40625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10657,10 +10657,10 @@
         <v>291</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D408" s="2" t="s">
         <v>292</v>
@@ -11301,10 +11301,10 @@
         <v>294</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D436" s="2" t="s">
         <v>295</v>
@@ -11945,10 +11945,10 @@
         <v>297</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D464" s="2" t="s">
         <v>298</v>
@@ -12589,10 +12589,10 @@
         <v>300</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D492" s="2" t="s">
         <v>301</v>
@@ -13233,10 +13233,10 @@
         <v>303</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D520" s="2" t="s">
         <v>304</v>
@@ -13877,10 +13877,10 @@
         <v>306</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D548" s="2" t="s">
         <v>304</v>
@@ -16338,10 +16338,10 @@
         <v>326</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="C655" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D655" s="2" t="s">
         <v>327</v>
@@ -16982,10 +16982,10 @@
         <v>329</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="C683" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D683" s="2" t="s">
         <v>327</v>
@@ -18949,7 +18949,7 @@
         <v>389</v>
       </c>
       <c r="F768" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G768" s="2" t="s">
         <v>59</v>

--- a/docs/Mapping_casi_uso/matrimoni/Matr_012.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_012.xlsx
@@ -8774,7 +8774,7 @@
         <v>221</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D326" s="2" t="s">
         <v>258</v>
